--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>6.38</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>6.38</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1357,68 +1357,68 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="O6" t="n">
-        <v>3.8</v>
+        <v>3.93</v>
       </c>
       <c r="P6" t="n">
-        <v>6</v>
+        <v>6.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1516,68 +1516,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="O7" t="n">
-        <v>3.93</v>
+        <v>3.8</v>
       </c>
       <c r="P7" t="n">
-        <v>6.38</v>
+        <v>6</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>6.38</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>6.38</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1516,68 +1516,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="O7" t="n">
-        <v>3.8</v>
+        <v>3.93</v>
       </c>
       <c r="P7" t="n">
-        <v>6</v>
+        <v>6.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,68 +1675,68 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="O8" t="n">
-        <v>3.93</v>
+        <v>3.8</v>
       </c>
       <c r="P8" t="n">
-        <v>6.38</v>
+        <v>6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1516,68 +1516,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="O7" t="n">
-        <v>3.93</v>
+        <v>3.8</v>
       </c>
       <c r="P7" t="n">
-        <v>6.38</v>
+        <v>6</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,68 +1675,68 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="O8" t="n">
-        <v>3.8</v>
+        <v>3.93</v>
       </c>
       <c r="P8" t="n">
-        <v>6</v>
+        <v>6.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1516,68 +1516,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="O7" t="n">
-        <v>3.8</v>
+        <v>3.93</v>
       </c>
       <c r="P7" t="n">
-        <v>6</v>
+        <v>6.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,68 +1675,68 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="O8" t="n">
-        <v>3.93</v>
+        <v>3.8</v>
       </c>
       <c r="P8" t="n">
-        <v>6.38</v>
+        <v>6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1357,68 +1357,68 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,68 +1675,68 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1357,68 +1357,68 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="O6" t="n">
-        <v>3.8</v>
+        <v>3.93</v>
       </c>
       <c r="P6" t="n">
-        <v>6</v>
+        <v>6.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>6.38</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,68 +1675,68 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1357,68 +1357,68 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="O6" t="n">
-        <v>3.93</v>
+        <v>3.8</v>
       </c>
       <c r="P6" t="n">
-        <v>6.38</v>
+        <v>6</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>6.38</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,68 +1675,68 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1357,68 +1357,68 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1516,68 +1516,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="O7" t="n">
-        <v>3.93</v>
+        <v>3.8</v>
       </c>
       <c r="P7" t="n">
-        <v>6.38</v>
+        <v>6</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>6.38</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1516,68 +1516,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="O7" t="n">
-        <v>3.8</v>
+        <v>3.93</v>
       </c>
       <c r="P7" t="n">
-        <v>6</v>
+        <v>6.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,68 +1675,68 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="O8" t="n">
-        <v>3.93</v>
+        <v>3.8</v>
       </c>
       <c r="P8" t="n">
-        <v>6.38</v>
+        <v>6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU12"/>
+  <dimension ref="A1:AU11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1516,68 +1516,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="O7" t="n">
-        <v>3.93</v>
+        <v>3.8</v>
       </c>
       <c r="P7" t="n">
-        <v>6.38</v>
+        <v>6</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,68 +1675,68 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="O8" t="n">
-        <v>3.8</v>
+        <v>3.93</v>
       </c>
       <c r="P8" t="n">
-        <v>6</v>
+        <v>6.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2259,165 +2259,6 @@
         <v>0</v>
       </c>
       <c r="AU11" s="3" t="n">
-        <v>46226.875</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>46226</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Botafogo SP</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Juventude</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" s="3" t="n">
         <v>46226.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1516,68 +1516,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="O7" t="n">
-        <v>3.8</v>
+        <v>3.93</v>
       </c>
       <c r="P7" t="n">
-        <v>6</v>
+        <v>6.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,68 +1675,68 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="O8" t="n">
-        <v>3.93</v>
+        <v>3.8</v>
       </c>
       <c r="P8" t="n">
-        <v>6.38</v>
+        <v>6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>6.38</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1516,68 +1516,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="O7" t="n">
-        <v>3.93</v>
+        <v>3.8</v>
       </c>
       <c r="P7" t="n">
-        <v>6.38</v>
+        <v>6</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,68 +1675,68 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G5" t="n">

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1357,68 +1357,68 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="O6" t="n">
-        <v>3.93</v>
+        <v>3.8</v>
       </c>
       <c r="P6" t="n">
-        <v>6.38</v>
+        <v>6</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1516,68 +1516,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>6.38</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>6.38</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>6.38</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1357,68 +1357,68 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,68 +1675,68 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1357,68 +1357,68 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>6.38</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,68 +1675,68 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="O8" t="n">
-        <v>3.8</v>
+        <v>3.93</v>
       </c>
       <c r="P8" t="n">
-        <v>6</v>
+        <v>6.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1357,68 +1357,68 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.55</v>
+        <v>2.22</v>
       </c>
       <c r="O6" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="P6" t="n">
-        <v>6</v>
+        <v>3.59</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>6.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,68 +1675,68 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="O8" t="n">
-        <v>3.93</v>
+        <v>3.8</v>
       </c>
       <c r="P8" t="n">
-        <v>6.38</v>
+        <v>6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2165,34 +2165,34 @@
         <v>3.04</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA11" t="n">
         <v>2.5</v>
@@ -2201,19 +2201,19 @@
         <v>1.47</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.22</v>
+        <v>1.59</v>
       </c>
       <c r="O6" t="n">
-        <v>3.1</v>
+        <v>3.93</v>
       </c>
       <c r="P6" t="n">
-        <v>3.59</v>
+        <v>6.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.59</v>
+        <v>2.22</v>
       </c>
       <c r="O7" t="n">
-        <v>3.93</v>
+        <v>3.1</v>
       </c>
       <c r="P7" t="n">
-        <v>6.38</v>
+        <v>3.59</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.59</v>
+        <v>2.22</v>
       </c>
       <c r="O6" t="n">
-        <v>3.93</v>
+        <v>3.1</v>
       </c>
       <c r="P6" t="n">
-        <v>6.38</v>
+        <v>3.59</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.22</v>
+        <v>1.59</v>
       </c>
       <c r="O7" t="n">
-        <v>3.1</v>
+        <v>3.93</v>
       </c>
       <c r="P7" t="n">
-        <v>3.59</v>
+        <v>6.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1516,68 +1516,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="O7" t="n">
-        <v>3.93</v>
+        <v>3.8</v>
       </c>
       <c r="P7" t="n">
-        <v>6.38</v>
+        <v>6</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T7" t="n">
-        <v>2.88</v>
+        <v>3.13</v>
       </c>
       <c r="U7" t="n">
-        <v>2.67</v>
+        <v>2.73</v>
       </c>
       <c r="V7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF7" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,68 +1675,68 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="O8" t="n">
-        <v>3.8</v>
+        <v>3.93</v>
       </c>
       <c r="P8" t="n">
-        <v>6</v>
+        <v>6.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T8" t="n">
-        <v>3.13</v>
+        <v>2.88</v>
       </c>
       <c r="U8" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1357,68 +1357,68 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.22</v>
+        <v>1.55</v>
       </c>
       <c r="O6" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="P6" t="n">
-        <v>3.59</v>
+        <v>6</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1516,68 +1516,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="O7" t="n">
-        <v>3.8</v>
+        <v>3.93</v>
       </c>
       <c r="P7" t="n">
-        <v>6</v>
+        <v>6.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T7" t="n">
-        <v>3.13</v>
+        <v>2.88</v>
       </c>
       <c r="U7" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.59</v>
+        <v>2.22</v>
       </c>
       <c r="O8" t="n">
-        <v>3.93</v>
+        <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>6.38</v>
+        <v>3.59</v>
       </c>
       <c r="Q8" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF8" t="n">
         <v>2.05</v>
       </c>
-      <c r="R8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2</v>
-      </c>
       <c r="AG8" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.47</v>
+        <v>1.7</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1847,55 +1847,55 @@
         <v>3.55</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.59</v>
+        <v>2.22</v>
       </c>
       <c r="O7" t="n">
-        <v>3.93</v>
+        <v>3.1</v>
       </c>
       <c r="P7" t="n">
-        <v>6.38</v>
+        <v>3.59</v>
       </c>
       <c r="Q7" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF7" t="n">
         <v>2.05</v>
       </c>
-      <c r="R7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2</v>
-      </c>
       <c r="AG7" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.47</v>
+        <v>1.7</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.22</v>
+        <v>1.59</v>
       </c>
       <c r="O8" t="n">
-        <v>3.1</v>
+        <v>3.93</v>
       </c>
       <c r="P8" t="n">
-        <v>3.59</v>
+        <v>6.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.64</v>
+        <v>2.05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="T8" t="n">
-        <v>2.58</v>
+        <v>2.88</v>
       </c>
       <c r="U8" t="n">
-        <v>3.15</v>
+        <v>2.67</v>
       </c>
       <c r="V8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
         <v>1.29</v>
       </c>
-      <c r="W8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.42</v>
-      </c>
       <c r="Z8" t="n">
-        <v>2.83</v>
+        <v>3.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.35</v>
+        <v>1.99</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.39</v>
+        <v>3.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.7</v>
+        <v>2.47</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1357,84 +1357,84 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.55</v>
+        <v>2.22</v>
       </c>
       <c r="O6" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="P6" t="n">
-        <v>6</v>
+        <v>3.59</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.15</v>
+        <v>2.64</v>
       </c>
       <c r="R6" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="S6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
         <v>1.35</v>
       </c>
-      <c r="T6" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK6" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1516,68 +1516,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.22</v>
+        <v>1.55</v>
       </c>
       <c r="O7" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="P7" t="n">
-        <v>3.59</v>
+        <v>6</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.64</v>
+        <v>2.15</v>
       </c>
       <c r="R7" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="S7" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="T7" t="n">
-        <v>2.58</v>
+        <v>3.13</v>
       </c>
       <c r="U7" t="n">
-        <v>3.15</v>
+        <v>2.73</v>
       </c>
       <c r="V7" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.83</v>
+        <v>3.24</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.35</v>
+        <v>1.96</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.39</v>
+        <v>3.12</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1052,55 +1052,55 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="R4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA4" t="n">
         <v>1.95</v>
       </c>
-      <c r="S4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AB4" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.75</v>
+        <v>3.35</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>2.5</v>
       </c>
-      <c r="O5" t="n">
-        <v>3</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3.1</v>
-      </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.35</v>
+        <v>4.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.22</v>
+        <v>1.59</v>
       </c>
       <c r="O6" t="n">
-        <v>3.1</v>
+        <v>3.93</v>
       </c>
       <c r="P6" t="n">
-        <v>3.59</v>
+        <v>6.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.64</v>
+        <v>2.05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="S6" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="T6" t="n">
-        <v>2.58</v>
+        <v>2.88</v>
       </c>
       <c r="U6" t="n">
-        <v>3.15</v>
+        <v>2.67</v>
       </c>
       <c r="V6" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y6" t="n">
         <v>1.29</v>
       </c>
-      <c r="W6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.42</v>
-      </c>
       <c r="Z6" t="n">
-        <v>2.83</v>
+        <v>3.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.35</v>
+        <v>1.99</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.39</v>
+        <v>3.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.7</v>
+        <v>2.47</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1516,84 +1516,84 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.55</v>
+        <v>2.22</v>
       </c>
       <c r="O7" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="P7" t="n">
-        <v>6</v>
+        <v>3.59</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.15</v>
+        <v>2.64</v>
       </c>
       <c r="R7" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="S7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.35</v>
       </c>
-      <c r="T7" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK7" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,68 +1675,68 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="O8" t="n">
-        <v>3.93</v>
+        <v>3.8</v>
       </c>
       <c r="P8" t="n">
-        <v>6.38</v>
+        <v>6</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T8" t="n">
-        <v>2.88</v>
+        <v>3.13</v>
       </c>
       <c r="U8" t="n">
-        <v>2.67</v>
+        <v>2.73</v>
       </c>
       <c r="V8" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF8" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.1</v>
+        <v>2.54</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="T4" t="n">
-        <v>2.75</v>
+        <v>2.31</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>3.46</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="W4" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.73</v>
+        <v>2.14</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>1.3</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.44</v>
+        <v>1.84</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.5</v>
+        <v>3.22</v>
       </c>
       <c r="R5" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="T5" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="U5" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
         <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.6</v>
+        <v>3.46</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.45</v>
+        <v>2.06</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.75</v>
+        <v>3.35</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.15</v>
+        <v>1.79</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.91</v>
+        <v>1.45</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1373,37 +1373,37 @@
         <v>2.05</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="S6" t="n">
         <v>1.36</v>
       </c>
       <c r="T6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.88</v>
       </c>
-      <c r="U6" t="n">
-        <v>2.67</v>
-      </c>
       <c r="V6" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AC6" t="n">
         <v>3.5</v>
@@ -1412,7 +1412,7 @@
         <v>1.3</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF6" t="n">
         <v>2</v>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1516,84 +1516,84 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.22</v>
+        <v>1.71</v>
       </c>
       <c r="O7" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="P7" t="n">
-        <v>3.59</v>
+        <v>4.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.64</v>
+        <v>2.05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="S7" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="T7" t="n">
-        <v>2.58</v>
+        <v>3.2</v>
       </c>
       <c r="U7" t="n">
-        <v>3.15</v>
+        <v>2.45</v>
       </c>
       <c r="V7" t="n">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.83</v>
+        <v>3.9</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.35</v>
+        <v>1.82</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.6</v>
+        <v>2.03</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.39</v>
+        <v>2.9</v>
       </c>
       <c r="AD7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.2</v>
       </c>
-      <c r="AE7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AK7" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,84 +1675,84 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="O8" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>6</v>
+        <v>3.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.15</v>
+        <v>2.65</v>
       </c>
       <c r="R8" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.35</v>
       </c>
-      <c r="T8" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK8" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1838,28 +1838,28 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P9" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="Q9" t="n">
         <v>2.7</v>
       </c>
       <c r="R9" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="T9" t="n">
-        <v>2.43</v>
+        <v>2.31</v>
       </c>
       <c r="U9" t="n">
-        <v>3.36</v>
+        <v>3.7</v>
       </c>
       <c r="V9" t="n">
         <v>1.25</v>
@@ -1868,25 +1868,25 @@
         <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>5</v>
+        <v>4.45</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE9" t="n">
         <v>1.01</v>
@@ -1895,7 +1895,7 @@
         <v>2.11</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2165,25 +2165,25 @@
         <v>3.04</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="S11" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="T11" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="U11" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="V11" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
         <v>1.07</v>
@@ -2192,25 +2192,25 @@
         <v>1.48</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.65</v>
+        <v>5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AG11" t="n">
         <v>1.7</v>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1516,84 +1516,84 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="O7" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="P7" t="n">
-        <v>4.6</v>
+        <v>3.86</v>
       </c>
       <c r="Q7" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="n">
         <v>2.05</v>
       </c>
-      <c r="R7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD7" t="n">
+      <c r="AG7" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.35</v>
       </c>
-      <c r="AE7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AK7" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,84 +1675,84 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="O8" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="P8" t="n">
-        <v>3.86</v>
+        <v>4.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.65</v>
+        <v>2.05</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="T8" t="n">
-        <v>2.56</v>
+        <v>3.2</v>
       </c>
       <c r="U8" t="n">
-        <v>3.28</v>
+        <v>2.45</v>
       </c>
       <c r="V8" t="n">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.35</v>
+        <v>1.82</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.63</v>
+        <v>2.03</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.47</v>
+        <v>2.9</v>
       </c>
       <c r="AD8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.2</v>
       </c>
-      <c r="AE8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AK8" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.54</v>
+        <v>3.22</v>
       </c>
       <c r="R4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG4" t="n">
         <v>1.9</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.62</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>1.3</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.84</v>
+        <v>1.45</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z5" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q5" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.46</v>
-      </c>
       <c r="AA5" t="n">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.79</v>
+        <v>2.14</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>1.3</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.45</v>
+        <v>1.84</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.59</v>
+        <v>1.95</v>
       </c>
       <c r="O6" t="n">
-        <v>3.93</v>
+        <v>3.1</v>
       </c>
       <c r="P6" t="n">
-        <v>6.38</v>
+        <v>3.86</v>
       </c>
       <c r="Q6" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="n">
         <v>2.05</v>
       </c>
-      <c r="R6" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2</v>
-      </c>
       <c r="AG6" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.45</v>
+        <v>1.7</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1516,84 +1516,84 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="O7" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="P7" t="n">
-        <v>3.86</v>
+        <v>4.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.65</v>
+        <v>2.05</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S7" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="T7" t="n">
-        <v>2.56</v>
+        <v>3.2</v>
       </c>
       <c r="U7" t="n">
-        <v>3.28</v>
+        <v>2.45</v>
       </c>
       <c r="V7" t="n">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.35</v>
+        <v>1.82</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.63</v>
+        <v>2.03</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.47</v>
+        <v>2.9</v>
       </c>
       <c r="AD7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.2</v>
       </c>
-      <c r="AE7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AK7" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,68 +1675,68 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="O8" t="n">
-        <v>3.75</v>
+        <v>3.93</v>
       </c>
       <c r="P8" t="n">
-        <v>4.6</v>
+        <v>6.38</v>
       </c>
       <c r="Q8" t="n">
         <v>2.05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T8" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="U8" t="n">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="V8" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE8" t="n">
         <v>1.11</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -1052,22 +1052,22 @@
         <v>2.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T4" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
         <v>1.04</v>
@@ -1076,31 +1076,31 @@
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.46</v>
+        <v>3.38</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1211,55 +1211,55 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.95</v>
+        <v>1.59</v>
       </c>
       <c r="O6" t="n">
-        <v>3.1</v>
+        <v>3.93</v>
       </c>
       <c r="P6" t="n">
-        <v>3.86</v>
+        <v>6.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.65</v>
+        <v>2.05</v>
       </c>
       <c r="R6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF6" t="n">
         <v>2</v>
       </c>
-      <c r="S6" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AG6" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.7</v>
+        <v>2.45</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1516,68 +1516,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="O7" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="P7" t="n">
-        <v>4.6</v>
+        <v>3.91</v>
       </c>
       <c r="Q7" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF7" t="n">
         <v>2.05</v>
       </c>
-      <c r="R7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AG7" t="n">
-        <v>2.15</v>
+        <v>1.81</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,68 +1675,68 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="O8" t="n">
-        <v>3.93</v>
+        <v>3.75</v>
       </c>
       <c r="P8" t="n">
-        <v>6.38</v>
+        <v>4.6</v>
       </c>
       <c r="Q8" t="n">
         <v>2.05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AC8" t="n">
         <v>2.9</v>
       </c>
-      <c r="U8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AD8" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE8" t="n">
         <v>1.11</v>
       </c>
       <c r="AF8" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1841,10 +1841,10 @@
         <v>1.95</v>
       </c>
       <c r="O9" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="P9" t="n">
-        <v>3.9</v>
+        <v>3.23</v>
       </c>
       <c r="Q9" t="n">
         <v>2.7</v>
@@ -1859,10 +1859,10 @@
         <v>2.31</v>
       </c>
       <c r="U9" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="V9" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W9" t="n">
         <v>1.01</v>
@@ -1871,31 +1871,31 @@
         <v>1.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF9" t="n">
         <v>2.11</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="O10" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P10" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="R10" t="n">
         <v>2.02</v>
@@ -2027,19 +2027,19 @@
         <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AC10" t="n">
         <v>4.07</v>
@@ -2051,10 +2051,10 @@
         <v>1.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2168,13 +2168,13 @@
         <v>3.2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="S11" t="n">
         <v>1.45</v>
       </c>
       <c r="T11" t="n">
-        <v>2.31</v>
+        <v>2.44</v>
       </c>
       <c r="U11" t="n">
         <v>3.6</v>
@@ -2186,7 +2186,7 @@
         <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
         <v>1.48</v>
@@ -2229,7 +2229,7 @@
         <v>1.33</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G5">
@@ -1133,55 +1133,55 @@
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>6.01</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1296,55 +1296,55 @@
         <v>6.38</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA6">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AB6">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="O7">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P7">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="Q7">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="R7">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S7">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
-        <v>3.13</v>
+        <v>2.85</v>
       </c>
       <c r="U7">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="V7">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W7">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z7">
-        <v>3.24</v>
+        <v>3.75</v>
       </c>
       <c r="AA7">
-        <v>1.96</v>
+        <v>1.74</v>
       </c>
       <c r="AB7">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AC7">
-        <v>3.12</v>
+        <v>2.9</v>
       </c>
       <c r="AD7">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE7">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF7">
-        <v>1.97</v>
+        <v>1.7</v>
       </c>
       <c r="AG7">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK7">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL10">
         <v>0</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -970,7 +970,7 @@
         <v>2.6</v>
       </c>
       <c r="Q4">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="R4">
         <v>1.98</v>
@@ -985,7 +985,7 @@
         <v>2.75</v>
       </c>
       <c r="V4">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="W4">
         <v>1.04</v>
@@ -1006,10 +1006,10 @@
         <v>1.66</v>
       </c>
       <c r="AC4">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="AD4">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE4">
         <v>1.08</v>
@@ -1157,31 +1157,31 @@
         <v>1.05</v>
       </c>
       <c r="Y5">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="Z5">
         <v>2.38</v>
       </c>
       <c r="AA5">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="AB5">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AC5">
-        <v>6.01</v>
+        <v>6.1</v>
       </c>
       <c r="AD5">
         <v>1.14</v>
       </c>
       <c r="AE5">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF5">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AG5">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.35</v>
       </c>
       <c r="AK5">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="O10">
         <v>3.25</v>
       </c>
       <c r="P10">
-        <v>3.8</v>
+        <v>4.13</v>
       </c>
       <c r="Q10">
         <v>2.45</v>
@@ -1972,10 +1972,10 @@
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z10">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="AA10">
         <v>2</v>
@@ -1984,13 +1984,13 @@
         <v>1.75</v>
       </c>
       <c r="AC10">
-        <v>4.07</v>
+        <v>3.5</v>
       </c>
       <c r="AD10">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE10">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF10">
         <v>1.81</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -964,61 +964,61 @@
         <v>2.45</v>
       </c>
       <c r="O4">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P4">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q4">
         <v>3.1</v>
       </c>
       <c r="R4">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="S4">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T4">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="U4">
-        <v>2.75</v>
+        <v>3.12</v>
       </c>
       <c r="V4">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W4">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y4">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z4">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="AA4">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AB4">
         <v>1.66</v>
       </c>
       <c r="AC4">
-        <v>3.35</v>
+        <v>3.96</v>
       </c>
       <c r="AD4">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AE4">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AF4">
         <v>1.8</v>
       </c>
       <c r="AG4">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1136,52 +1136,52 @@
         <v>2.5</v>
       </c>
       <c r="R5">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="S5">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T5">
         <v>2.5</v>
       </c>
       <c r="U5">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="V5">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W5">
         <v>1.04</v>
       </c>
       <c r="X5">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y5">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="Z5">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="AA5">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="AB5">
         <v>1.53</v>
       </c>
       <c r="AC5">
-        <v>6.1</v>
+        <v>4.64</v>
       </c>
       <c r="AD5">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE5">
         <v>1.05</v>
       </c>
       <c r="AF5">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AG5">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AK5">
         <v>1.83</v>
@@ -1939,31 +1939,31 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="O10">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P10">
-        <v>4.13</v>
+        <v>4</v>
       </c>
       <c r="Q10">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="R10">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="S10">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="T10">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="U10">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="V10">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W10">
         <v>1.05</v>
@@ -1972,25 +1972,25 @@
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z10">
-        <v>3.04</v>
+        <v>3.42</v>
       </c>
       <c r="AA10">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AB10">
         <v>1.75</v>
       </c>
       <c r="AC10">
-        <v>3.5</v>
+        <v>4.32</v>
       </c>
       <c r="AD10">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE10">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF10">
         <v>1.81</v>
@@ -2012,7 +2012,7 @@
         <v>1.25</v>
       </c>
       <c r="AK10">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AL10">
         <v>0</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -970,10 +970,10 @@
         <v>2.7</v>
       </c>
       <c r="Q4">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R4">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="S4">
         <v>1.4</v>
@@ -991,16 +991,16 @@
         <v>1.06</v>
       </c>
       <c r="X4">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z4">
-        <v>3.25</v>
+        <v>2.97</v>
       </c>
       <c r="AA4">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AB4">
         <v>1.66</v>
@@ -1009,16 +1009,16 @@
         <v>3.96</v>
       </c>
       <c r="AD4">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AE4">
         <v>1.02</v>
       </c>
       <c r="AF4">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG4">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R5">
         <v>1.92</v>
@@ -1142,7 +1142,7 @@
         <v>1.5</v>
       </c>
       <c r="T5">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="U5">
         <v>3.5</v>
@@ -1163,19 +1163,19 @@
         <v>2.65</v>
       </c>
       <c r="AA5">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="AB5">
         <v>1.53</v>
       </c>
       <c r="AC5">
-        <v>4.64</v>
+        <v>5.98</v>
       </c>
       <c r="AD5">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE5">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF5">
         <v>2.14</v>
@@ -1296,10 +1296,10 @@
         <v>6.38</v>
       </c>
       <c r="Q6">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R6">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="S6">
         <v>1.36</v>
@@ -1308,40 +1308,40 @@
         <v>2.9</v>
       </c>
       <c r="U6">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="V6">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W6">
+        <v>1.06</v>
+      </c>
+      <c r="X6">
         <v>1.05</v>
       </c>
-      <c r="X6">
-        <v>1.03</v>
-      </c>
       <c r="Y6">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Z6">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="AA6">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AB6">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC6">
         <v>3.4</v>
       </c>
       <c r="AD6">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE6">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF6">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AG6">
         <v>1.7</v>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK6">
         <v>2.45</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="O7">
         <v>3.75</v>
       </c>
       <c r="P7">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="Q7">
         <v>2.05</v>
@@ -1465,10 +1465,10 @@
         <v>2.2</v>
       </c>
       <c r="S7">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T7">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="U7">
         <v>2.45</v>
@@ -1477,28 +1477,28 @@
         <v>1.44</v>
       </c>
       <c r="W7">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
         <v>1.21</v>
       </c>
       <c r="Z7">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="AA7">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AB7">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AC7">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="AD7">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE7">
         <v>1.1</v>
@@ -1613,19 +1613,19 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="O8">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="P8">
-        <v>3.91</v>
+        <v>3.28</v>
       </c>
       <c r="Q8">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="R8">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="S8">
         <v>1.49</v>
@@ -1634,28 +1634,28 @@
         <v>2.41</v>
       </c>
       <c r="U8">
-        <v>3.15</v>
+        <v>3.28</v>
       </c>
       <c r="V8">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W8">
         <v>1</v>
       </c>
       <c r="X8">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y8">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z8">
-        <v>2.62</v>
+        <v>2.95</v>
       </c>
       <c r="AA8">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AB8">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AC8">
         <v>4.47</v>
@@ -1667,7 +1667,7 @@
         <v>1.01</v>
       </c>
       <c r="AF8">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AG8">
         <v>1.81</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK8">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="O9">
-        <v>2.81</v>
+        <v>3.04</v>
       </c>
       <c r="P9">
-        <v>3.23</v>
+        <v>3.7</v>
       </c>
       <c r="Q9">
         <v>2.7</v>
@@ -1800,19 +1800,19 @@
         <v>3.6</v>
       </c>
       <c r="V9">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W9">
         <v>1.01</v>
       </c>
       <c r="X9">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y9">
         <v>1.49</v>
       </c>
       <c r="Z9">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="AA9">
         <v>2.38</v>
@@ -1824,16 +1824,16 @@
         <v>4.5</v>
       </c>
       <c r="AD9">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE9">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF9">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AG9">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AK9">
         <v>1.79</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="O10">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P10">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="Q10">
         <v>2.38</v>
@@ -1963,10 +1963,10 @@
         <v>3.1</v>
       </c>
       <c r="V10">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W10">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
         <v>1.01</v>
@@ -1975,13 +1975,13 @@
         <v>1.33</v>
       </c>
       <c r="Z10">
-        <v>3.42</v>
+        <v>3.05</v>
       </c>
       <c r="AA10">
         <v>2.04</v>
       </c>
       <c r="AB10">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AC10">
         <v>4.32</v>
@@ -1990,13 +1990,13 @@
         <v>1.23</v>
       </c>
       <c r="AE10">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF10">
         <v>1.81</v>
       </c>
       <c r="AG10">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2111,16 +2111,16 @@
         <v>3.04</v>
       </c>
       <c r="Q11">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R11">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="S11">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="T11">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="U11">
         <v>3.6</v>
@@ -2129,16 +2129,16 @@
         <v>1.25</v>
       </c>
       <c r="W11">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X11">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
         <v>1.48</v>
       </c>
       <c r="Z11">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="AA11">
         <v>2.45</v>
@@ -2147,16 +2147,16 @@
         <v>1.5</v>
       </c>
       <c r="AC11">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AD11">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AE11">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF11">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AG11">
         <v>1.7</v>
@@ -2175,7 +2175,7 @@
         <v>1.33</v>
       </c>
       <c r="AK11">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AL11">
         <v>0</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G6">
@@ -1283,84 +1283,84 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N6">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="O6">
-        <v>3.93</v>
+        <v>3.75</v>
       </c>
       <c r="P6">
-        <v>6.38</v>
+        <v>5.05</v>
       </c>
       <c r="Q6">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R6">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="S6">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T6">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="U6">
-        <v>2.93</v>
+        <v>2.45</v>
       </c>
       <c r="V6">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
         <v>1.06</v>
       </c>
       <c r="X6">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="Z6">
-        <v>3.48</v>
+        <v>3.62</v>
       </c>
       <c r="AA6">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="AB6">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AC6">
-        <v>3.4</v>
+        <v>2.76</v>
       </c>
       <c r="AD6">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AE6">
         <v>1.1</v>
       </c>
       <c r="AF6">
+        <v>1.7</v>
+      </c>
+      <c r="AG6">
+        <v>2.05</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
+        <v>1.2</v>
+      </c>
+      <c r="AK6">
         <v>2</v>
-      </c>
-      <c r="AG6">
-        <v>1.7</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.23</v>
-      </c>
-      <c r="AK6">
-        <v>2.45</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G7">
@@ -1446,69 +1446,69 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N7">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="O7">
-        <v>3.75</v>
+        <v>3.93</v>
       </c>
       <c r="P7">
-        <v>5.05</v>
+        <v>6.38</v>
       </c>
       <c r="Q7">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R7">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="S7">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T7">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="U7">
-        <v>2.45</v>
+        <v>2.93</v>
       </c>
       <c r="V7">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W7">
         <v>1.06</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y7">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="Z7">
-        <v>3.62</v>
+        <v>3.48</v>
       </c>
       <c r="AA7">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="AB7">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AC7">
-        <v>2.76</v>
+        <v>3.4</v>
       </c>
       <c r="AD7">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE7">
         <v>1.1</v>
       </c>
       <c r="AF7">
+        <v>2</v>
+      </c>
+      <c r="AG7">
         <v>1.7</v>
       </c>
-      <c r="AG7">
-        <v>2.05</v>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK7">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AL7">
         <v>0</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G6">
@@ -1283,69 +1283,69 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N6">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="O6">
-        <v>3.75</v>
+        <v>3.93</v>
       </c>
       <c r="P6">
-        <v>5.05</v>
+        <v>6.38</v>
       </c>
       <c r="Q6">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R6">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="S6">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T6">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="U6">
-        <v>2.45</v>
+        <v>2.93</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W6">
         <v>1.06</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y6">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="Z6">
-        <v>3.62</v>
+        <v>3.48</v>
       </c>
       <c r="AA6">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="AB6">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AC6">
-        <v>2.76</v>
+        <v>3.4</v>
       </c>
       <c r="AD6">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE6">
         <v>1.1</v>
       </c>
       <c r="AF6">
+        <v>2</v>
+      </c>
+      <c r="AG6">
         <v>1.7</v>
       </c>
-      <c r="AG6">
-        <v>2.05</v>
-      </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK6">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G7">
@@ -1446,84 +1446,84 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N7">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="O7">
-        <v>3.93</v>
+        <v>3.75</v>
       </c>
       <c r="P7">
-        <v>6.38</v>
+        <v>5.05</v>
       </c>
       <c r="Q7">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R7">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="S7">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T7">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="U7">
-        <v>2.93</v>
+        <v>2.45</v>
       </c>
       <c r="V7">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W7">
         <v>1.06</v>
       </c>
       <c r="X7">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="Z7">
-        <v>3.48</v>
+        <v>3.62</v>
       </c>
       <c r="AA7">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="AB7">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AC7">
-        <v>3.4</v>
+        <v>2.76</v>
       </c>
       <c r="AD7">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AE7">
         <v>1.1</v>
       </c>
       <c r="AF7">
+        <v>1.7</v>
+      </c>
+      <c r="AG7">
+        <v>2.05</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
+        <v>1.2</v>
+      </c>
+      <c r="AK7">
         <v>2</v>
-      </c>
-      <c r="AG7">
-        <v>1.7</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.23</v>
-      </c>
-      <c r="AK7">
-        <v>2.45</v>
       </c>
       <c r="AL7">
         <v>0</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -674,10 +674,10 @@
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G6">
@@ -1283,69 +1283,69 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N6">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="O6">
-        <v>3.75</v>
+        <v>3.93</v>
       </c>
       <c r="P6">
-        <v>5.05</v>
+        <v>6.38</v>
       </c>
       <c r="Q6">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R6">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="S6">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T6">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="U6">
-        <v>2.45</v>
+        <v>2.93</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W6">
         <v>1.06</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y6">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="Z6">
-        <v>3.62</v>
+        <v>3.48</v>
       </c>
       <c r="AA6">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="AB6">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AC6">
-        <v>2.76</v>
+        <v>3.4</v>
       </c>
       <c r="AD6">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE6">
         <v>1.1</v>
       </c>
       <c r="AF6">
+        <v>2</v>
+      </c>
+      <c r="AG6">
         <v>1.7</v>
       </c>
-      <c r="AG6">
-        <v>2.05</v>
-      </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK6">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G7">
@@ -1446,84 +1446,84 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N7">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="O7">
-        <v>3.93</v>
+        <v>3.75</v>
       </c>
       <c r="P7">
-        <v>6.38</v>
+        <v>5.05</v>
       </c>
       <c r="Q7">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R7">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="S7">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T7">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="U7">
-        <v>2.93</v>
+        <v>2.45</v>
       </c>
       <c r="V7">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W7">
         <v>1.06</v>
       </c>
       <c r="X7">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="Z7">
-        <v>3.48</v>
+        <v>3.62</v>
       </c>
       <c r="AA7">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="AB7">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AC7">
-        <v>3.4</v>
+        <v>2.76</v>
       </c>
       <c r="AD7">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AE7">
         <v>1.1</v>
       </c>
       <c r="AF7">
+        <v>1.7</v>
+      </c>
+      <c r="AG7">
+        <v>2.05</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
+        <v>1.2</v>
+      </c>
+      <c r="AK7">
         <v>2</v>
-      </c>
-      <c r="AG7">
-        <v>1.7</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.23</v>
-      </c>
-      <c r="AK7">
-        <v>2.45</v>
       </c>
       <c r="AL7">
         <v>0</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="O6">
-        <v>3.93</v>
+        <v>3.71</v>
       </c>
       <c r="P6">
-        <v>6.38</v>
+        <v>3.9</v>
       </c>
       <c r="Q6">
+        <v>2.31</v>
+      </c>
+      <c r="R6">
+        <v>2.39</v>
+      </c>
+      <c r="S6">
+        <v>1.38</v>
+      </c>
+      <c r="T6">
+        <v>2.81</v>
+      </c>
+      <c r="U6">
+        <v>2.45</v>
+      </c>
+      <c r="V6">
+        <v>1.44</v>
+      </c>
+      <c r="W6">
+        <v>1.08</v>
+      </c>
+      <c r="X6">
+        <v>1.03</v>
+      </c>
+      <c r="Y6">
+        <v>1.21</v>
+      </c>
+      <c r="Z6">
+        <v>3.9</v>
+      </c>
+      <c r="AA6">
+        <v>1.8</v>
+      </c>
+      <c r="AB6">
         <v>2</v>
       </c>
-      <c r="R6">
-        <v>2.19</v>
-      </c>
-      <c r="S6">
-        <v>1.36</v>
-      </c>
-      <c r="T6">
-        <v>2.9</v>
-      </c>
-      <c r="U6">
-        <v>2.93</v>
-      </c>
-      <c r="V6">
-        <v>1.39</v>
-      </c>
-      <c r="W6">
-        <v>1.06</v>
-      </c>
-      <c r="X6">
-        <v>1.05</v>
-      </c>
-      <c r="Y6">
-        <v>1.31</v>
-      </c>
-      <c r="Z6">
-        <v>3.48</v>
-      </c>
-      <c r="AA6">
-        <v>1.97</v>
-      </c>
-      <c r="AB6">
-        <v>1.83</v>
-      </c>
       <c r="AC6">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AD6">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AE6">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF6">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AG6">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK6">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G7">
@@ -1446,69 +1446,69 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N7">
+        <v>1.42</v>
+      </c>
+      <c r="O7">
+        <v>4.06</v>
+      </c>
+      <c r="P7">
+        <v>6.5</v>
+      </c>
+      <c r="Q7">
+        <v>2</v>
+      </c>
+      <c r="R7">
+        <v>2.1</v>
+      </c>
+      <c r="S7">
+        <v>1.39</v>
+      </c>
+      <c r="T7">
+        <v>2.66</v>
+      </c>
+      <c r="U7">
+        <v>2.9</v>
+      </c>
+      <c r="V7">
+        <v>1.37</v>
+      </c>
+      <c r="W7">
+        <v>1.04</v>
+      </c>
+      <c r="X7">
+        <v>1.03</v>
+      </c>
+      <c r="Y7">
+        <v>1.29</v>
+      </c>
+      <c r="Z7">
+        <v>3.4</v>
+      </c>
+      <c r="AA7">
+        <v>1.98</v>
+      </c>
+      <c r="AB7">
+        <v>1.85</v>
+      </c>
+      <c r="AC7">
+        <v>3.4</v>
+      </c>
+      <c r="AD7">
+        <v>1.29</v>
+      </c>
+      <c r="AE7">
+        <v>1.06</v>
+      </c>
+      <c r="AF7">
+        <v>2.04</v>
+      </c>
+      <c r="AG7">
         <v>1.75</v>
       </c>
-      <c r="O7">
-        <v>3.75</v>
-      </c>
-      <c r="P7">
-        <v>5.05</v>
-      </c>
-      <c r="Q7">
-        <v>2.05</v>
-      </c>
-      <c r="R7">
-        <v>2.2</v>
-      </c>
-      <c r="S7">
-        <v>1.38</v>
-      </c>
-      <c r="T7">
-        <v>2.81</v>
-      </c>
-      <c r="U7">
-        <v>2.45</v>
-      </c>
-      <c r="V7">
-        <v>1.44</v>
-      </c>
-      <c r="W7">
-        <v>1.06</v>
-      </c>
-      <c r="X7">
-        <v>1.01</v>
-      </c>
-      <c r="Y7">
-        <v>1.21</v>
-      </c>
-      <c r="Z7">
-        <v>3.62</v>
-      </c>
-      <c r="AA7">
-        <v>1.8</v>
-      </c>
-      <c r="AB7">
-        <v>2</v>
-      </c>
-      <c r="AC7">
-        <v>2.76</v>
-      </c>
-      <c r="AD7">
-        <v>1.35</v>
-      </c>
-      <c r="AE7">
-        <v>1.1</v>
-      </c>
-      <c r="AF7">
-        <v>1.7</v>
-      </c>
-      <c r="AG7">
-        <v>2.05</v>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK7">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AL7">
         <v>0</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.14</v>
+        <v>3.93</v>
       </c>
       <c r="O2">
-        <v>3.41</v>
+        <v>3.22</v>
       </c>
       <c r="P2">
-        <v>2.18</v>
+        <v>1.97</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="AA2">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AB2">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,65 +798,65 @@
         </is>
       </c>
       <c r="N3">
+        <v>1.35</v>
+      </c>
+      <c r="O3">
+        <v>4.47</v>
+      </c>
+      <c r="P3">
+        <v>7.31</v>
+      </c>
+      <c r="Q3">
+        <v>1.91</v>
+      </c>
+      <c r="R3">
+        <v>2.2</v>
+      </c>
+      <c r="S3">
+        <v>1.4</v>
+      </c>
+      <c r="T3">
+        <v>2.47</v>
+      </c>
+      <c r="U3">
+        <v>2.97</v>
+      </c>
+      <c r="V3">
+        <v>1.31</v>
+      </c>
+      <c r="W3">
+        <v>1.05</v>
+      </c>
+      <c r="X3">
+        <v>1.05</v>
+      </c>
+      <c r="Y3">
+        <v>1.34</v>
+      </c>
+      <c r="Z3">
+        <v>3.28</v>
+      </c>
+      <c r="AA3">
+        <v>2.07</v>
+      </c>
+      <c r="AB3">
+        <v>1.73</v>
+      </c>
+      <c r="AC3">
+        <v>4.1</v>
+      </c>
+      <c r="AD3">
+        <v>1.25</v>
+      </c>
+      <c r="AE3">
+        <v>1.07</v>
+      </c>
+      <c r="AF3">
+        <v>2.38</v>
+      </c>
+      <c r="AG3">
         <v>1.53</v>
       </c>
-      <c r="O3">
-        <v>3.87</v>
-      </c>
-      <c r="P3">
-        <v>6.34</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>0</v>
-      </c>
-      <c r="Y3">
-        <v>0</v>
-      </c>
-      <c r="Z3">
-        <v>0</v>
-      </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0</v>
-      </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>0</v>
-      </c>
-      <c r="AG3">
-        <v>0</v>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>[]</t>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,25 +961,25 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="O4">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P4">
         <v>2.7</v>
       </c>
       <c r="Q4">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="R4">
-        <v>2.16</v>
+        <v>1.9</v>
       </c>
       <c r="S4">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T4">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="U4">
         <v>3.12</v>
@@ -988,37 +988,37 @@
         <v>1.29</v>
       </c>
       <c r="W4">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z4">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="AA4">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AB4">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC4">
-        <v>3.96</v>
+        <v>4.2</v>
       </c>
       <c r="AD4">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AE4">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF4">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AG4">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AK4">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q5">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="R5">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="S5">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="T5">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="U5">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="V5">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W5">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X5">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y5">
         <v>1.46</v>
       </c>
       <c r="Z5">
-        <v>2.65</v>
+        <v>2.08</v>
       </c>
       <c r="AA5">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AB5">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC5">
-        <v>5.98</v>
+        <v>6.33</v>
       </c>
       <c r="AD5">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AE5">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF5">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AG5">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="AK5">
         <v>1.83</v>
@@ -1613,28 +1613,28 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="O8">
         <v>2.88</v>
       </c>
       <c r="P8">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="Q8">
         <v>2.72</v>
       </c>
       <c r="R8">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S8">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T8">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="U8">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="V8">
         <v>1.28</v>
@@ -1643,34 +1643,34 @@
         <v>1</v>
       </c>
       <c r="X8">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="Z8">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="AA8">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="AB8">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AC8">
-        <v>4.47</v>
+        <v>4.25</v>
       </c>
       <c r="AD8">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE8">
         <v>1.01</v>
       </c>
       <c r="AF8">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AG8">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK8">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,19 +1776,19 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="O9">
-        <v>3.04</v>
+        <v>2.81</v>
       </c>
       <c r="P9">
-        <v>3.7</v>
+        <v>3.23</v>
       </c>
       <c r="Q9">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="R9">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="S9">
         <v>1.56</v>
@@ -1797,43 +1797,43 @@
         <v>2.31</v>
       </c>
       <c r="U9">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="V9">
         <v>1.25</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X9">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Y9">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Z9">
         <v>2.7</v>
       </c>
       <c r="AA9">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AB9">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AC9">
         <v>4.5</v>
       </c>
       <c r="AD9">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE9">
         <v>1.01</v>
       </c>
       <c r="AF9">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG9">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK9">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="O10">
-        <v>3.7</v>
+        <v>3.03</v>
       </c>
       <c r="P10">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="Q10">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R10">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="S10">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T10">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U10">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="V10">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W10">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z10">
-        <v>3.05</v>
+        <v>3.38</v>
       </c>
       <c r="AA10">
-        <v>2.04</v>
+        <v>1.83</v>
       </c>
       <c r="AB10">
         <v>1.68</v>
       </c>
       <c r="AC10">
-        <v>4.32</v>
+        <v>3.5</v>
       </c>
       <c r="AD10">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE10">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF10">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="AG10">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK10">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.53</v>
+        <v>2.37</v>
       </c>
       <c r="O11">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="P11">
-        <v>3.04</v>
+        <v>2.73</v>
       </c>
       <c r="Q11">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="R11">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="S11">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="T11">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="U11">
         <v>3.6</v>
       </c>
       <c r="V11">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W11">
         <v>1.01</v>
       </c>
       <c r="X11">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="Y11">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="Z11">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="AA11">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AB11">
         <v>1.5</v>
       </c>
       <c r="AC11">
-        <v>4.7</v>
+        <v>5.26</v>
       </c>
       <c r="AD11">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AE11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF11">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="AG11">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK11">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL11">
         <v>0</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.93</v>
+        <v>1.34</v>
       </c>
       <c r="O2">
-        <v>3.22</v>
+        <v>4.52</v>
       </c>
       <c r="P2">
-        <v>1.97</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q2">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="R2">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="S2">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T2">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U2">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="V2">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="W2">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X2">
         <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="Z2">
-        <v>3.43</v>
+        <v>3.26</v>
       </c>
       <c r="AA2">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="AB2">
         <v>1.74</v>
       </c>
       <c r="AC2">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="AD2">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE2">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF2">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="AG2">
-        <v>1.89</v>
+        <v>1.45</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.8</v>
+        <v>1.17</v>
       </c>
       <c r="AK2">
-        <v>1.2</v>
+        <v>2.88</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G3">
@@ -798,80 +798,80 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.35</v>
+        <v>3.97</v>
       </c>
       <c r="O3">
-        <v>4.47</v>
+        <v>3.1</v>
       </c>
       <c r="P3">
-        <v>7.31</v>
+        <v>1.83</v>
       </c>
       <c r="Q3">
-        <v>1.91</v>
+        <v>4.65</v>
       </c>
       <c r="R3">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="S3">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T3">
         <v>2.47</v>
       </c>
       <c r="U3">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="V3">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W3">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X3">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z3">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="AA3">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="AB3">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC3">
-        <v>4.1</v>
+        <v>3.72</v>
       </c>
       <c r="AD3">
+        <v>1.27</v>
+      </c>
+      <c r="AE3">
+        <v>1.06</v>
+      </c>
+      <c r="AF3">
+        <v>1.81</v>
+      </c>
+      <c r="AG3">
+        <v>1.86</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3">
         <v>1.25</v>
       </c>
-      <c r="AE3">
-        <v>1.07</v>
-      </c>
-      <c r="AF3">
-        <v>2.38</v>
-      </c>
-      <c r="AG3">
-        <v>1.53</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3">
-        <v>1.17</v>
-      </c>
       <c r="AK3">
-        <v>3</v>
+        <v>1.22</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.73</v>
+        <v>1.42</v>
       </c>
       <c r="O6">
-        <v>3.71</v>
+        <v>4.1</v>
       </c>
       <c r="P6">
-        <v>3.9</v>
+        <v>6</v>
       </c>
       <c r="Q6">
-        <v>2.31</v>
+        <v>2.05</v>
       </c>
       <c r="R6">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="S6">
+        <v>1.39</v>
+      </c>
+      <c r="T6">
+        <v>2.77</v>
+      </c>
+      <c r="U6">
+        <v>2.81</v>
+      </c>
+      <c r="V6">
         <v>1.38</v>
       </c>
-      <c r="T6">
-        <v>2.81</v>
-      </c>
-      <c r="U6">
-        <v>2.45</v>
-      </c>
-      <c r="V6">
-        <v>1.44</v>
-      </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X6">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y6">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="Z6">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="AA6">
+        <v>1.91</v>
+      </c>
+      <c r="AB6">
         <v>1.8</v>
       </c>
-      <c r="AB6">
-        <v>2</v>
-      </c>
       <c r="AC6">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AD6">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AE6">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF6">
-        <v>1.7</v>
+        <v>2.04</v>
       </c>
       <c r="AG6">
-        <v>2.05</v>
+        <v>1.71</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK6">
-        <v>2.1</v>
+        <v>2.53</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.42</v>
+        <v>1.76</v>
       </c>
       <c r="O7">
-        <v>4.06</v>
+        <v>3.71</v>
       </c>
       <c r="P7">
-        <v>6.5</v>
+        <v>5.05</v>
       </c>
       <c r="Q7">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="R7">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S7">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T7">
-        <v>2.66</v>
+        <v>3.23</v>
       </c>
       <c r="U7">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="V7">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W7">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z7">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AA7">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="AB7">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AC7">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="AD7">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AE7">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF7">
-        <v>2.04</v>
+        <v>1.7</v>
       </c>
       <c r="AG7">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK7">
-        <v>2.5</v>
+        <v>2.06</v>
       </c>
       <c r="AL7">
         <v>0</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.34</v>
+        <v>3.97</v>
       </c>
       <c r="O2">
-        <v>4.52</v>
+        <v>3.1</v>
       </c>
       <c r="P2">
-        <v>9.699999999999999</v>
+        <v>1.83</v>
       </c>
       <c r="Q2">
-        <v>1.8</v>
+        <v>4.65</v>
       </c>
       <c r="R2">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="S2">
         <v>1.44</v>
       </c>
       <c r="T2">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="U2">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="V2">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W2">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X2">
         <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z2">
-        <v>3.26</v>
+        <v>3.32</v>
       </c>
       <c r="AA2">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AB2">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC2">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="AD2">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AE2">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF2">
-        <v>2.3</v>
+        <v>1.81</v>
       </c>
       <c r="AG2">
-        <v>1.45</v>
+        <v>1.86</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK2">
-        <v>2.88</v>
+        <v>1.22</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>3.97</v>
+        <v>1.34</v>
       </c>
       <c r="O3">
-        <v>3.1</v>
+        <v>4.52</v>
       </c>
       <c r="P3">
-        <v>1.83</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q3">
-        <v>4.65</v>
+        <v>1.8</v>
       </c>
       <c r="R3">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="S3">
         <v>1.44</v>
       </c>
       <c r="T3">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="U3">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="V3">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W3">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
         <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z3">
-        <v>3.32</v>
+        <v>3.26</v>
       </c>
       <c r="AA3">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AB3">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AC3">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="AD3">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AE3">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF3">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="AG3">
-        <v>1.86</v>
+        <v>1.45</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK3">
-        <v>1.22</v>
+        <v>2.88</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -964,40 +964,40 @@
         <v>2.28</v>
       </c>
       <c r="O4">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="P4">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="Q4">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="R4">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="S4">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="T4">
-        <v>2.69</v>
+        <v>2.12</v>
       </c>
       <c r="U4">
-        <v>3.12</v>
+        <v>2.42</v>
       </c>
       <c r="V4">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="W4">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X4">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z4">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="AA4">
         <v>2.2</v>
@@ -1006,19 +1006,19 @@
         <v>1.65</v>
       </c>
       <c r="AC4">
-        <v>4.2</v>
+        <v>4.78</v>
       </c>
       <c r="AD4">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AE4">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF4">
         <v>1.83</v>
       </c>
       <c r="AG4">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AK4">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,31 +1124,31 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="O5">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="P5">
-        <v>4.1</v>
+        <v>4.72</v>
       </c>
       <c r="Q5">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="R5">
         <v>1.9</v>
       </c>
       <c r="S5">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="T5">
         <v>2.43</v>
       </c>
       <c r="U5">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="V5">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W5">
         <v>1.02</v>
@@ -1163,13 +1163,13 @@
         <v>2.08</v>
       </c>
       <c r="AA5">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AB5">
         <v>1.5</v>
       </c>
       <c r="AC5">
-        <v>6.33</v>
+        <v>6.36</v>
       </c>
       <c r="AD5">
         <v>1.12</v>
@@ -1178,10 +1178,10 @@
         <v>1.05</v>
       </c>
       <c r="AF5">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AG5">
-        <v>1.45</v>
+        <v>1.61</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.1</v>
       </c>
       <c r="AK5">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>2.02</v>
       </c>
       <c r="O8">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="P8">
         <v>3.6</v>
@@ -1646,7 +1646,7 @@
         <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z8">
         <v>2.62</v>
@@ -1655,19 +1655,19 @@
         <v>2.39</v>
       </c>
       <c r="AB8">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AC8">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="AD8">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF8">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG8">
         <v>1.7</v>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK8">
         <v>1.73</v>
@@ -1779,31 +1779,31 @@
         <v>1.95</v>
       </c>
       <c r="O9">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="P9">
-        <v>3.23</v>
+        <v>4.1</v>
       </c>
       <c r="Q9">
-        <v>2.72</v>
+        <v>2.65</v>
       </c>
       <c r="R9">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="S9">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="T9">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="U9">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="V9">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W9">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X9">
         <v>1.06</v>
@@ -1812,13 +1812,13 @@
         <v>1.48</v>
       </c>
       <c r="Z9">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AA9">
         <v>2.35</v>
       </c>
       <c r="AB9">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AC9">
         <v>4.5</v>
@@ -1833,7 +1833,7 @@
         <v>2.1</v>
       </c>
       <c r="AG9">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK9">
         <v>1.75</v>
@@ -1942,55 +1942,55 @@
         <v>1.8</v>
       </c>
       <c r="O10">
-        <v>3.03</v>
+        <v>3.25</v>
       </c>
       <c r="P10">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="Q10">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="R10">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="S10">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="T10">
-        <v>2.75</v>
+        <v>2.16</v>
       </c>
       <c r="U10">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V10">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W10">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="Z10">
-        <v>3.38</v>
+        <v>2.92</v>
       </c>
       <c r="AA10">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="AB10">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AC10">
         <v>3.5</v>
       </c>
       <c r="AD10">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE10">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF10">
         <v>1.89</v>
@@ -2102,55 +2102,55 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.37</v>
+        <v>2.28</v>
       </c>
       <c r="O11">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="P11">
-        <v>2.73</v>
+        <v>2.87</v>
       </c>
       <c r="Q11">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="R11">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="S11">
+        <v>1.56</v>
+      </c>
+      <c r="T11">
+        <v>2.45</v>
+      </c>
+      <c r="U11">
+        <v>3.4</v>
+      </c>
+      <c r="V11">
+        <v>1.29</v>
+      </c>
+      <c r="W11">
+        <v>1.04</v>
+      </c>
+      <c r="X11">
+        <v>1.08</v>
+      </c>
+      <c r="Y11">
         <v>1.5</v>
-      </c>
-      <c r="T11">
-        <v>2.27</v>
-      </c>
-      <c r="U11">
-        <v>3.6</v>
-      </c>
-      <c r="V11">
-        <v>1.22</v>
-      </c>
-      <c r="W11">
-        <v>1.01</v>
-      </c>
-      <c r="X11">
-        <v>1.12</v>
-      </c>
-      <c r="Y11">
-        <v>1.51</v>
       </c>
       <c r="Z11">
         <v>2.47</v>
       </c>
       <c r="AA11">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="AB11">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AC11">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="AD11">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AE11">
         <v>1.04</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -964,13 +964,13 @@
         <v>2.28</v>
       </c>
       <c r="O4">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="P4">
-        <v>2.69</v>
+        <v>2.93</v>
       </c>
       <c r="Q4">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="R4">
         <v>2.16</v>
@@ -979,13 +979,13 @@
         <v>1.37</v>
       </c>
       <c r="T4">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="U4">
         <v>2.42</v>
       </c>
       <c r="V4">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W4">
         <v>1.04</v>
@@ -1006,7 +1006,7 @@
         <v>1.65</v>
       </c>
       <c r="AC4">
-        <v>4.78</v>
+        <v>4.8</v>
       </c>
       <c r="AD4">
         <v>1.2</v>
@@ -1124,31 +1124,31 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="O5">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P5">
-        <v>4.72</v>
+        <v>4.83</v>
       </c>
       <c r="Q5">
         <v>2.45</v>
       </c>
       <c r="R5">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="S5">
         <v>1.43</v>
       </c>
       <c r="T5">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="U5">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="V5">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W5">
         <v>1.02</v>
@@ -1160,16 +1160,16 @@
         <v>1.46</v>
       </c>
       <c r="Z5">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AA5">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AB5">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AC5">
-        <v>6.36</v>
+        <v>4.5</v>
       </c>
       <c r="AD5">
         <v>1.12</v>
@@ -1178,7 +1178,7 @@
         <v>1.05</v>
       </c>
       <c r="AF5">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG5">
         <v>1.61</v>
@@ -1287,16 +1287,16 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="O6">
         <v>4.1</v>
       </c>
       <c r="P6">
-        <v>6</v>
+        <v>6.48</v>
       </c>
       <c r="Q6">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R6">
         <v>2.2</v>
@@ -1305,34 +1305,34 @@
         <v>1.39</v>
       </c>
       <c r="T6">
-        <v>2.77</v>
+        <v>2.99</v>
       </c>
       <c r="U6">
-        <v>2.81</v>
+        <v>2.94</v>
       </c>
       <c r="V6">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W6">
         <v>1.04</v>
       </c>
       <c r="X6">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
         <v>1.3</v>
       </c>
       <c r="Z6">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="AA6">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AB6">
         <v>1.8</v>
       </c>
       <c r="AC6">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AD6">
         <v>1.29</v>
@@ -1341,10 +1341,10 @@
         <v>1.06</v>
       </c>
       <c r="AF6">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AG6">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AK6">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,58 +1450,58 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="O7">
-        <v>3.71</v>
+        <v>3.55</v>
       </c>
       <c r="P7">
-        <v>5.05</v>
+        <v>4.4</v>
       </c>
       <c r="Q7">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="R7">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="S7">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T7">
-        <v>3.23</v>
+        <v>3.3</v>
       </c>
       <c r="U7">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="V7">
         <v>1.44</v>
       </c>
       <c r="W7">
+        <v>1.06</v>
+      </c>
+      <c r="X7">
+        <v>1.02</v>
+      </c>
+      <c r="Y7">
+        <v>1.21</v>
+      </c>
+      <c r="Z7">
+        <v>3.9</v>
+      </c>
+      <c r="AA7">
+        <v>1.78</v>
+      </c>
+      <c r="AB7">
+        <v>1.98</v>
+      </c>
+      <c r="AC7">
+        <v>2.99</v>
+      </c>
+      <c r="AD7">
+        <v>1.4</v>
+      </c>
+      <c r="AE7">
         <v>1.09</v>
-      </c>
-      <c r="X7">
-        <v>1.01</v>
-      </c>
-      <c r="Y7">
-        <v>1.22</v>
-      </c>
-      <c r="Z7">
-        <v>3.8</v>
-      </c>
-      <c r="AA7">
-        <v>1.83</v>
-      </c>
-      <c r="AB7">
-        <v>2.02</v>
-      </c>
-      <c r="AC7">
-        <v>2.8</v>
-      </c>
-      <c r="AD7">
-        <v>1.34</v>
-      </c>
-      <c r="AE7">
-        <v>1.12</v>
       </c>
       <c r="AF7">
         <v>1.7</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK7">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>2.02</v>
       </c>
       <c r="O8">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="P8">
         <v>3.6</v>
@@ -1628,13 +1628,13 @@
         <v>2</v>
       </c>
       <c r="S8">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="T8">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="U8">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="V8">
         <v>1.28</v>
@@ -1652,10 +1652,10 @@
         <v>2.62</v>
       </c>
       <c r="AA8">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="AB8">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AC8">
         <v>4.6</v>
@@ -1794,13 +1794,13 @@
         <v>1.5</v>
       </c>
       <c r="T9">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="U9">
-        <v>3.45</v>
+        <v>3.36</v>
       </c>
       <c r="V9">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W9">
         <v>1.04</v>
@@ -1954,16 +1954,16 @@
         <v>2.15</v>
       </c>
       <c r="S10">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T10">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="U10">
         <v>2.9</v>
       </c>
       <c r="V10">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W10">
         <v>1.04</v>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="O11">
         <v>2.95</v>
@@ -2117,16 +2117,16 @@
         <v>1.98</v>
       </c>
       <c r="S11">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="T11">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="U11">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="V11">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W11">
         <v>1.04</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -1613,16 +1613,16 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="O8">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="P8">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="Q8">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="R8">
         <v>2</v>
@@ -1646,10 +1646,10 @@
         <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="Z8">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AA8">
         <v>2.3</v>
@@ -1658,13 +1658,13 @@
         <v>1.6</v>
       </c>
       <c r="AC8">
-        <v>4.6</v>
+        <v>4.25</v>
       </c>
       <c r="AD8">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF8">
         <v>2.05</v>
@@ -1779,13 +1779,13 @@
         <v>1.95</v>
       </c>
       <c r="O9">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P9">
         <v>4.1</v>
       </c>
       <c r="Q9">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="R9">
         <v>2</v>
@@ -1794,7 +1794,7 @@
         <v>1.5</v>
       </c>
       <c r="T9">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="U9">
         <v>3.36</v>
@@ -1812,22 +1812,22 @@
         <v>1.48</v>
       </c>
       <c r="Z9">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="AA9">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="AB9">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AC9">
         <v>4.5</v>
       </c>
       <c r="AD9">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AE9">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF9">
         <v>2.1</v>
@@ -1849,7 +1849,7 @@
         <v>1.3</v>
       </c>
       <c r="AK9">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="O11">
         <v>2.95</v>
@@ -2141,13 +2141,13 @@
         <v>2.47</v>
       </c>
       <c r="AA11">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="AB11">
         <v>1.48</v>
       </c>
       <c r="AC11">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AD11">
         <v>1.11</v>
@@ -2175,7 +2175,7 @@
         <v>1.36</v>
       </c>
       <c r="AK11">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AL11">
         <v>0</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -635,77 +635,77 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.97</v>
+        <v>3.5</v>
       </c>
       <c r="O2">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P2">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="Q2">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="R2">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="S2">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T2">
-        <v>2.47</v>
+        <v>2.88</v>
       </c>
       <c r="U2">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="V2">
         <v>1.33</v>
       </c>
       <c r="W2">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X2">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y2">
+        <v>1.34</v>
+      </c>
+      <c r="Z2">
+        <v>3.28</v>
+      </c>
+      <c r="AA2">
+        <v>2.07</v>
+      </c>
+      <c r="AB2">
+        <v>1.7</v>
+      </c>
+      <c r="AC2">
+        <v>3.96</v>
+      </c>
+      <c r="AD2">
+        <v>1.25</v>
+      </c>
+      <c r="AE2">
+        <v>1.07</v>
+      </c>
+      <c r="AF2">
+        <v>1.83</v>
+      </c>
+      <c r="AG2">
+        <v>1.87</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ2">
         <v>1.33</v>
-      </c>
-      <c r="Z2">
-        <v>3.32</v>
-      </c>
-      <c r="AA2">
-        <v>2.01</v>
-      </c>
-      <c r="AB2">
-        <v>1.75</v>
-      </c>
-      <c r="AC2">
-        <v>3.72</v>
-      </c>
-      <c r="AD2">
-        <v>1.27</v>
-      </c>
-      <c r="AE2">
-        <v>1.06</v>
-      </c>
-      <c r="AF2">
-        <v>1.81</v>
-      </c>
-      <c r="AG2">
-        <v>1.86</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2">
-        <v>1.25</v>
       </c>
       <c r="AK2">
         <v>1.22</v>
@@ -801,61 +801,61 @@
         <v>1.34</v>
       </c>
       <c r="O3">
-        <v>4.52</v>
+        <v>4.33</v>
       </c>
       <c r="P3">
-        <v>9.699999999999999</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Q3">
         <v>1.8</v>
       </c>
       <c r="R3">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="S3">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T3">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U3">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="V3">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W3">
         <v>1.05</v>
       </c>
       <c r="X3">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y3">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z3">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="AA3">
         <v>2.03</v>
       </c>
       <c r="AB3">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AC3">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AD3">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE3">
         <v>1.08</v>
       </c>
       <c r="AF3">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AG3">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AK3">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="O4">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="P4">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="Q4">
         <v>2.95</v>
@@ -991,13 +991,13 @@
         <v>1.04</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y4">
         <v>1.4</v>
       </c>
       <c r="Z4">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AA4">
         <v>2.2</v>
@@ -1006,19 +1006,19 @@
         <v>1.65</v>
       </c>
       <c r="AC4">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="AD4">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE4">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AF4">
         <v>1.83</v>
       </c>
       <c r="AG4">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK4">
         <v>1.44</v>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="O5">
         <v>3.2</v>
@@ -1142,10 +1142,10 @@
         <v>1.43</v>
       </c>
       <c r="T5">
-        <v>2.46</v>
+        <v>2</v>
       </c>
       <c r="U5">
-        <v>3.46</v>
+        <v>2.75</v>
       </c>
       <c r="V5">
         <v>1.2</v>
@@ -1160,10 +1160,10 @@
         <v>1.46</v>
       </c>
       <c r="Z5">
-        <v>2.1</v>
+        <v>2.58</v>
       </c>
       <c r="AA5">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="AB5">
         <v>1.51</v>
@@ -1175,13 +1175,13 @@
         <v>1.12</v>
       </c>
       <c r="AE5">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF5">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AG5">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1287,16 +1287,16 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="O6">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P6">
-        <v>6.48</v>
+        <v>6.65</v>
       </c>
       <c r="Q6">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R6">
         <v>2.2</v>
@@ -1308,7 +1308,7 @@
         <v>2.99</v>
       </c>
       <c r="U6">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="V6">
         <v>1.4</v>
@@ -1344,7 +1344,7 @@
         <v>2.02</v>
       </c>
       <c r="AG6">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>1.1</v>
       </c>
       <c r="AK6">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1459,49 +1459,49 @@
         <v>4.4</v>
       </c>
       <c r="Q7">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="R7">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S7">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="T7">
-        <v>3.3</v>
+        <v>2.77</v>
       </c>
       <c r="U7">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="V7">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W7">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
         <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z7">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AA7">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AB7">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AC7">
-        <v>2.99</v>
+        <v>3.12</v>
       </c>
       <c r="AD7">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE7">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF7">
         <v>1.7</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK7">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="O10">
         <v>3.25</v>
       </c>
       <c r="P10">
-        <v>3.42</v>
+        <v>3.99</v>
       </c>
       <c r="Q10">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="R10">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="S10">
         <v>1.36</v>
@@ -1960,7 +1960,7 @@
         <v>2.15</v>
       </c>
       <c r="U10">
-        <v>2.9</v>
+        <v>2.38</v>
       </c>
       <c r="V10">
         <v>1.28</v>
@@ -1969,7 +1969,7 @@
         <v>1.04</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y10">
         <v>1.31</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="O6">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="P6">
-        <v>6.65</v>
+        <v>4.4</v>
       </c>
       <c r="Q6">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="R6">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S6">
         <v>1.39</v>
       </c>
       <c r="T6">
-        <v>2.99</v>
+        <v>2.77</v>
       </c>
       <c r="U6">
-        <v>2.96</v>
+        <v>2.65</v>
       </c>
       <c r="V6">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W6">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z6">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="AA6">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="AB6">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AC6">
-        <v>3.45</v>
+        <v>3.12</v>
       </c>
       <c r="AD6">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE6">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF6">
-        <v>2.02</v>
+        <v>1.7</v>
       </c>
       <c r="AG6">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AK6">
-        <v>2.63</v>
+        <v>2.06</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="O7">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="P7">
-        <v>4.4</v>
+        <v>6.65</v>
       </c>
       <c r="Q7">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="R7">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S7">
         <v>1.39</v>
       </c>
       <c r="T7">
-        <v>2.77</v>
+        <v>2.99</v>
       </c>
       <c r="U7">
-        <v>2.65</v>
+        <v>2.96</v>
       </c>
       <c r="V7">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y7">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z7">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="AA7">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="AB7">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AC7">
-        <v>3.12</v>
+        <v>3.45</v>
       </c>
       <c r="AD7">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE7">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF7">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="AG7">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AK7">
-        <v>2.06</v>
+        <v>2.63</v>
       </c>
       <c r="AL7">
         <v>0</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -641,58 +641,58 @@
         <v>3.2</v>
       </c>
       <c r="P2">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q2">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="R2">
         <v>1.94</v>
       </c>
       <c r="S2">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T2">
-        <v>2.88</v>
+        <v>2.47</v>
       </c>
       <c r="U2">
         <v>2.92</v>
       </c>
       <c r="V2">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W2">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X2">
         <v>1.06</v>
       </c>
       <c r="Y2">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z2">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="AA2">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AB2">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC2">
-        <v>3.96</v>
+        <v>3.78</v>
       </c>
       <c r="AD2">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE2">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF2">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AG2">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AK2">
         <v>1.22</v>
@@ -804,16 +804,16 @@
         <v>4.33</v>
       </c>
       <c r="P3">
-        <v>9.949999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="Q3">
         <v>1.8</v>
       </c>
       <c r="R3">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="S3">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T3">
         <v>2.88</v>
@@ -825,7 +825,7 @@
         <v>1.36</v>
       </c>
       <c r="W3">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X3">
         <v>1.05</v>
@@ -840,22 +840,22 @@
         <v>2.03</v>
       </c>
       <c r="AB3">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC3">
-        <v>3.34</v>
+        <v>3.85</v>
       </c>
       <c r="AD3">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE3">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF3">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AG3">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AK3">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,43 +961,43 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="O4">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="P4">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="Q4">
         <v>2.95</v>
       </c>
       <c r="R4">
-        <v>2.16</v>
+        <v>1.96</v>
       </c>
       <c r="S4">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="T4">
-        <v>2.13</v>
+        <v>2.44</v>
       </c>
       <c r="U4">
-        <v>2.42</v>
+        <v>3.3</v>
       </c>
       <c r="V4">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W4">
         <v>1.04</v>
       </c>
       <c r="X4">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z4">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AA4">
         <v>2.2</v>
@@ -1006,19 +1006,19 @@
         <v>1.65</v>
       </c>
       <c r="AC4">
-        <v>3</v>
+        <v>4.82</v>
       </c>
       <c r="AD4">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE4">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AF4">
         <v>1.83</v>
       </c>
       <c r="AG4">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AK4">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="O5">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="P5">
-        <v>4.83</v>
+        <v>4.1</v>
       </c>
       <c r="Q5">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="R5">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="S5">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="T5">
-        <v>2</v>
+        <v>2.63</v>
       </c>
       <c r="U5">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="V5">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="W5">
         <v>1.02</v>
       </c>
       <c r="X5">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="Z5">
-        <v>2.58</v>
+        <v>2.81</v>
       </c>
       <c r="AA5">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="AB5">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AC5">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AD5">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AE5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF5">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="AG5">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AK5">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,80 +1287,80 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="O6">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="P6">
-        <v>4.4</v>
+        <v>6.48</v>
       </c>
       <c r="Q6">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="R6">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S6">
         <v>1.39</v>
       </c>
       <c r="T6">
-        <v>2.77</v>
+        <v>2.68</v>
       </c>
       <c r="U6">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="V6">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
+        <v>1.27</v>
+      </c>
+      <c r="Z6">
+        <v>3.18</v>
+      </c>
+      <c r="AA6">
+        <v>1.95</v>
+      </c>
+      <c r="AB6">
+        <v>1.85</v>
+      </c>
+      <c r="AC6">
+        <v>3.24</v>
+      </c>
+      <c r="AD6">
+        <v>1.26</v>
+      </c>
+      <c r="AE6">
+        <v>1.06</v>
+      </c>
+      <c r="AF6">
+        <v>2.02</v>
+      </c>
+      <c r="AG6">
+        <v>1.75</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
         <v>1.22</v>
       </c>
-      <c r="Z6">
-        <v>3.6</v>
-      </c>
-      <c r="AA6">
-        <v>1.77</v>
-      </c>
-      <c r="AB6">
-        <v>1.94</v>
-      </c>
-      <c r="AC6">
-        <v>3.12</v>
-      </c>
-      <c r="AD6">
-        <v>1.33</v>
-      </c>
-      <c r="AE6">
-        <v>1.08</v>
-      </c>
-      <c r="AF6">
-        <v>1.7</v>
-      </c>
-      <c r="AG6">
-        <v>2.05</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.2</v>
-      </c>
       <c r="AK6">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,65 +1450,65 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="O7">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="P7">
-        <v>6.65</v>
+        <v>4</v>
       </c>
       <c r="Q7">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="R7">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="S7">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T7">
-        <v>2.99</v>
+        <v>2.77</v>
       </c>
       <c r="U7">
-        <v>2.96</v>
+        <v>2.53</v>
       </c>
       <c r="V7">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W7">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X7">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z7">
-        <v>3.18</v>
+        <v>4</v>
       </c>
       <c r="AA7">
+        <v>1.89</v>
+      </c>
+      <c r="AB7">
+        <v>1.89</v>
+      </c>
+      <c r="AC7">
+        <v>2.89</v>
+      </c>
+      <c r="AD7">
+        <v>1.32</v>
+      </c>
+      <c r="AE7">
+        <v>1.14</v>
+      </c>
+      <c r="AF7">
+        <v>1.75</v>
+      </c>
+      <c r="AG7">
         <v>1.97</v>
       </c>
-      <c r="AB7">
-        <v>1.8</v>
-      </c>
-      <c r="AC7">
-        <v>3.45</v>
-      </c>
-      <c r="AD7">
-        <v>1.29</v>
-      </c>
-      <c r="AE7">
-        <v>1.06</v>
-      </c>
-      <c r="AF7">
-        <v>2.02</v>
-      </c>
-      <c r="AG7">
-        <v>1.73</v>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.1</v>
+        <v>1.31</v>
       </c>
       <c r="AK7">
-        <v>2.63</v>
+        <v>2</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="O8">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="P8">
-        <v>3.9</v>
+        <v>3.28</v>
       </c>
       <c r="Q8">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="R8">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="S8">
         <v>1.45</v>
       </c>
       <c r="T8">
-        <v>2.36</v>
+        <v>2.55</v>
       </c>
       <c r="U8">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="V8">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="W8">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X8">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y8">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="Z8">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AA8">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AB8">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC8">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="AD8">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AE8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF8">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG8">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK8">
         <v>1.73</v>
@@ -1776,61 +1776,61 @@
         </is>
       </c>
       <c r="N9">
+        <v>2.04</v>
+      </c>
+      <c r="O9">
+        <v>3.02</v>
+      </c>
+      <c r="P9">
+        <v>3.23</v>
+      </c>
+      <c r="Q9">
+        <v>2.73</v>
+      </c>
+      <c r="R9">
         <v>1.95</v>
       </c>
-      <c r="O9">
-        <v>3.05</v>
-      </c>
-      <c r="P9">
-        <v>4.1</v>
-      </c>
-      <c r="Q9">
-        <v>2.67</v>
-      </c>
-      <c r="R9">
-        <v>2</v>
-      </c>
       <c r="S9">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="T9">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="U9">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="V9">
         <v>1.25</v>
       </c>
       <c r="W9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y9">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="Z9">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="AA9">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AB9">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AC9">
-        <v>4.5</v>
+        <v>5.27</v>
       </c>
       <c r="AD9">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AE9">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF9">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AG9">
         <v>1.64</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AK9">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="O10">
-        <v>3.25</v>
+        <v>3.03</v>
       </c>
       <c r="P10">
-        <v>3.99</v>
+        <v>3.42</v>
       </c>
       <c r="Q10">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="R10">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="S10">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T10">
-        <v>2.15</v>
+        <v>2.66</v>
       </c>
       <c r="U10">
-        <v>2.38</v>
+        <v>3.19</v>
       </c>
       <c r="V10">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="W10">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X10">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="Z10">
-        <v>2.92</v>
+        <v>3.38</v>
       </c>
       <c r="AA10">
         <v>2.06</v>
       </c>
       <c r="AB10">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AC10">
-        <v>3.5</v>
+        <v>4.51</v>
       </c>
       <c r="AD10">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE10">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF10">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AG10">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AK10">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.37</v>
+        <v>2.49</v>
       </c>
       <c r="O11">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="P11">
-        <v>2.87</v>
+        <v>3.06</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -2117,65 +2117,65 @@
         <v>1.98</v>
       </c>
       <c r="S11">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="T11">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="U11">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="V11">
         <v>1.25</v>
       </c>
       <c r="W11">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X11">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Y11">
+        <v>1.51</v>
+      </c>
+      <c r="Z11">
+        <v>2.35</v>
+      </c>
+      <c r="AA11">
+        <v>2.43</v>
+      </c>
+      <c r="AB11">
+        <v>1.51</v>
+      </c>
+      <c r="AC11">
+        <v>4.8</v>
+      </c>
+      <c r="AD11">
+        <v>1.12</v>
+      </c>
+      <c r="AE11">
+        <v>1.02</v>
+      </c>
+      <c r="AF11">
+        <v>2.03</v>
+      </c>
+      <c r="AG11">
+        <v>1.7</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11">
+        <v>1.33</v>
+      </c>
+      <c r="AK11">
         <v>1.5</v>
-      </c>
-      <c r="Z11">
-        <v>2.47</v>
-      </c>
-      <c r="AA11">
-        <v>2.69</v>
-      </c>
-      <c r="AB11">
-        <v>1.48</v>
-      </c>
-      <c r="AC11">
-        <v>5.25</v>
-      </c>
-      <c r="AD11">
-        <v>1.11</v>
-      </c>
-      <c r="AE11">
-        <v>1.04</v>
-      </c>
-      <c r="AF11">
-        <v>2.06</v>
-      </c>
-      <c r="AG11">
-        <v>1.68</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11">
-        <v>1.36</v>
-      </c>
-      <c r="AK11">
-        <v>1.42</v>
       </c>
       <c r="AL11">
         <v>0</v>

--- a/jogos_2026-07-23.xlsx
+++ b/jogos_2026-07-23.xlsx
@@ -612,26 +612,26 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
@@ -696,12 +696,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+3"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["2", "77"]</t>
         </is>
       </c>
       <c r="AJ2">
@@ -714,28 +714,28 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -775,16 +775,16 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -794,7 +794,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
@@ -859,12 +859,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["15"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19"]</t>
         </is>
       </c>
       <c r="AJ3">
@@ -877,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -964,10 +964,10 @@
         <v>2.28</v>
       </c>
       <c r="O4">
-        <v>3.03</v>
+        <v>2.89</v>
       </c>
       <c r="P4">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="Q4">
         <v>2.95</v>
@@ -979,10 +979,10 @@
         <v>1.46</v>
       </c>
       <c r="T4">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="U4">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="V4">
         <v>1.33</v>
@@ -991,25 +991,25 @@
         <v>1.04</v>
       </c>
       <c r="X4">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z4">
-        <v>3.25</v>
+        <v>2.81</v>
       </c>
       <c r="AA4">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="AB4">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AC4">
-        <v>4.82</v>
+        <v>3.9</v>
       </c>
       <c r="AD4">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE4">
         <v>1.02</v>
@@ -1018,7 +1018,7 @@
         <v>1.83</v>
       </c>
       <c r="AG4">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.34</v>
       </c>
       <c r="AK4">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="O5">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="P5">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="Q5">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="R5">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S5">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="T5">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="U5">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="V5">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W5">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X5">
+        <v>1.05</v>
+      </c>
+      <c r="Y5">
+        <v>1.37</v>
+      </c>
+      <c r="Z5">
+        <v>2.66</v>
+      </c>
+      <c r="AA5">
+        <v>2.31</v>
+      </c>
+      <c r="AB5">
+        <v>1.57</v>
+      </c>
+      <c r="AC5">
+        <v>4.5</v>
+      </c>
+      <c r="AD5">
+        <v>1.17</v>
+      </c>
+      <c r="AE5">
         <v>1.03</v>
       </c>
-      <c r="Y5">
-        <v>1.43</v>
-      </c>
-      <c r="Z5">
-        <v>2.81</v>
-      </c>
-      <c r="AA5">
-        <v>2.3</v>
-      </c>
-      <c r="AB5">
-        <v>1.6</v>
-      </c>
-      <c r="AC5">
-        <v>4.2</v>
-      </c>
-      <c r="AD5">
-        <v>1.15</v>
-      </c>
-      <c r="AE5">
-        <v>1.02</v>
-      </c>
       <c r="AF5">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AG5">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AK5">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="O10">
-        <v>3.03</v>
+        <v>3.63</v>
       </c>
       <c r="P10">
-        <v>3.42</v>
+        <v>4.45</v>
       </c>
       <c r="Q10">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="R10">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="S10">
         <v>1.39</v>
@@ -1960,7 +1960,7 @@
         <v>2.66</v>
       </c>
       <c r="U10">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="V10">
         <v>1.35</v>
@@ -1972,31 +1972,31 @@
         <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z10">
-        <v>3.38</v>
+        <v>2.45</v>
       </c>
       <c r="AA10">
-        <v>2.06</v>
+        <v>1.82</v>
       </c>
       <c r="AB10">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC10">
-        <v>4.51</v>
+        <v>3.68</v>
       </c>
       <c r="AD10">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE10">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF10">
         <v>1.75</v>
       </c>
       <c r="AG10">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AK10">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AL10">
         <v>0</v>
